--- a/SDI_alignment_comparison_table.xlsx
+++ b/SDI_alignment_comparison_table.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,17 +487,25 @@
           <t>lateralorbitofrontal_1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.71</v>
+      </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.2</v>
+      </c>
       <c r="H4" t="n">
-        <v>-2.65</v>
+        <v>-1.71</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>-1.08</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="5">
@@ -509,17 +517,29 @@
           <t>lateralorbitofrontal_2</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.92</v>
+      </c>
       <c r="H5" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>-0.82</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1</v>
+      </c>
       <c r="J5" t="n">
-        <v>-0.51</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -528,18 +548,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>parstriangularis_1</t>
+          <t>parsorbitalis_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.3</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>0.31</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.3</v>
+      </c>
       <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -548,20 +574,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rostralanteriorcingulate_1</t>
+          <t>frontalpole_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>0.45</v>
+      </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
-        <v>-0.68</v>
-      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -570,19 +596,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>caudalanteriorcingulate_1</t>
+          <t>medialorbitofrontal_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>-0.68</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+        <v>-0.98</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -590,19 +626,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>posteriorcingulate_1</t>
+          <t>parstriangularis_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>-0.34</v>
+      </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-1.2</v>
+        <v>-0.34</v>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>-0.25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -610,19 +652,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>lateraloccipital_3</t>
+          <t>rostralmiddlefrontal_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>-0.68</v>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -630,22 +674,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>parahippocampal_1</t>
+          <t>superiorfrontal_4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
-        <v>-0.91</v>
-      </c>
+      <c r="F11" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
-        <v>-0.91</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>-0.55</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="12">
@@ -654,16 +696,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>inferiortemporal_1</t>
+          <t>paracentral_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>-0.77</v>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-0.33</v>
+        <v>-0.77</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -674,19 +718,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>transversetemporal_1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>rostralanteriorcingulate_1</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.23</v>
+      </c>
       <c r="H13" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+        <v>-0.31</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -694,17 +752,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>insula_1</t>
+          <t>caudalanteriorcingulate_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>-0.08</v>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>-0.08</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
     </row>
@@ -714,21 +774,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>insula_2</t>
+          <t>posteriorcingulate_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>-0.88</v>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-1.9</v>
+        <v>-0.88</v>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>-1.68</v>
-      </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -736,20 +796,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Right-Amygdala</t>
+          <t>isthmuscingulate_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>-0.13</v>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
-        <v>-2.51</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -758,22 +818,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Right-Hippocampus</t>
+          <t>pericalcarine_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="n">
-        <v>-1.23</v>
-      </c>
+      <c r="D17" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="n">
-        <v>-1.51</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -782,17 +840,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>lateralorbitofrontal_1</t>
+          <t>lateraloccipital_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>0.1</v>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>0.1</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
     </row>
@@ -802,20 +862,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>lateralorbitofrontal_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>fusiform_2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.1</v>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+        <v>-1.11</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>-1.1</v>
+      </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>-1.11</v>
+      </c>
       <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -824,18 +888,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>medialorbitofrontal_1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>parahippocampal_1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>-0.64</v>
+      </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>-0.62</v>
+      </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>-0.64</v>
+      </c>
       <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -844,21 +914,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>parstriangularis_1</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="n">
-        <v>-2.29</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>inferiortemporal_1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>-0.2</v>
+      </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>-0.36</v>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>-0.2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -866,19 +940,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>parsopercularis_1</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>inferiortemporal_2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>0.66</v>
+      </c>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0.68</v>
+      </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0.66</v>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>0.68</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -886,25 +966,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>parahippocampal_1</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>-1.59</v>
-      </c>
+          <t>middletemporal_2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>-0.32</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>-0.32</v>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -912,17 +992,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>temporalpole_1</t>
+          <t>bankssts_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
-        <v>-1.21</v>
+        <v>-0.13</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>-0.13</v>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
     </row>
@@ -932,19 +1014,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>superiortemporal_2</t>
+          <t>superiortemporal_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>-0.08</v>
+      </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0.22</v>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -952,17 +1040,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>insula_1</t>
+          <t>transversetemporal_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>-0.14</v>
+      </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>-0.88</v>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>-0.14</v>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
     </row>
@@ -972,22 +1062,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Left-Amygdala</t>
+          <t>insula_1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-2.11</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-1.65</v>
-      </c>
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>-2.15</v>
+        <v>-0.16</v>
       </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>-0.16</v>
+      </c>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -996,27 +1088,823 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>insula_2</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Right-Amygdala</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Right-Hippocampus</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>lateralorbitofrontal_1</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>lateralorbitofrontal_2</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>parsorbitalis_1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>medialorbitofrontal_1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>parstriangularis_1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>parsopercularis_1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>rostralmiddlefrontal_1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>rostralmiddlefrontal_2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>superiorfrontal_2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>superiorfrontal_4</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>caudalmiddlefrontal_1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>rostralanteriorcingulate_1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>postcentral_3</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>precuneus_2</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>lateraloccipital_2</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>fusiform_1</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>fusiform_2</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="J47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>parahippocampal_1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>entorhinal_1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>temporalpole_1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="n">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>inferiortemporal_2</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>middletemporal_2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>superiortemporal_1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="J53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>superiortemporal_2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>transversetemporal_1</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="J55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>insula_1</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="J56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>insula_2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Left-Amygdala</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="J58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>Left-Hippocampus</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="J28" t="n">
-        <v>-0.57</v>
-      </c>
+      <c r="C59" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="J59" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
